--- a/TestFiles/ExcelFiles/CaseRateLengthStay.xlsx
+++ b/TestFiles/ExcelFiles/CaseRateLengthStay.xlsx
@@ -101,7 +101,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>8.14</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="2">
@@ -109,7 +109,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>8.33</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="3">
@@ -117,7 +117,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>6.61</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="4">
@@ -125,7 +125,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>9.17</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="5">
@@ -133,7 +133,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3.05</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="6">
@@ -141,7 +141,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>10.65</v>
+        <v>8.79</v>
       </c>
     </row>
     <row r="7">
@@ -149,7 +149,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>3.92</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="8">
@@ -157,7 +157,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>9.72</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="9">
@@ -165,7 +165,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>8.8</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="10">
@@ -173,7 +173,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>10.89</v>
+        <v>6.64</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/CaseRateLengthStay.xlsx
+++ b/TestFiles/ExcelFiles/CaseRateLengthStay.xlsx
@@ -101,7 +101,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>8.29</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="2">
@@ -109,7 +109,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>11.81</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="3">
@@ -117,7 +117,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>8.43</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="4">
@@ -125,7 +125,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>11.23</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="5">
@@ -133,7 +133,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>4.48</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="6">
@@ -141,7 +141,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>7.21</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="7">
@@ -149,7 +149,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>12.35</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="8">
@@ -157,7 +157,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>6.12</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="9">
@@ -165,7 +165,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>10.82</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="10">
@@ -173,7 +173,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>11.47</v>
+        <v>10.74</v>
       </c>
     </row>
   </sheetData>
